--- a/Estudiando para el primer parcial/Mapeos.xlsx
+++ b/Estudiando para el primer parcial/Mapeos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rmc\Materias\INF 321 - Base de datos 1\INF-312\Estudiando para el primer parcial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8AC4B77-2432-4BCD-9BFF-6E83CC406EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00738724-372B-4F38-B459-C5E654801D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{1477E9CB-896E-499A-9AEE-89B5874AFFA7}"/>
   </bookViews>
@@ -237,15 +237,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,7 +603,7 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -618,16 +615,16 @@
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -639,7 +636,7 @@
       <c r="L3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O3" s="1" t="s">
@@ -651,7 +648,7 @@
       <c r="Q3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="T3" s="1" t="s">
@@ -912,22 +909,22 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="4" t="s">
         <v>35</v>
       </c>
     </row>
@@ -967,7 +964,7 @@
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -976,48 +973,46 @@
       <c r="C3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="Q3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="U3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="V3" s="1" t="s">
         <v>47</v>
       </c>
       <c r="X3" s="1" t="s">
@@ -1031,14 +1026,12 @@
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="2"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="2"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -1054,14 +1047,12 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="2"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="2"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -1077,14 +1068,12 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="2"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="2"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -1100,14 +1089,12 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="2"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="2"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -1123,14 +1110,12 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="2"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="2"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -1146,14 +1131,12 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="2"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="M9" s="2"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -1169,14 +1152,12 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="M10" s="2"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -1192,14 +1173,12 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="2"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-      <c r="M11" s="2"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
@@ -1215,14 +1194,12 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="2"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="M12" s="2"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
@@ -1238,14 +1215,12 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
-      <c r="M13" s="2"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
